--- a/examples/output/phase0-write-example.xlsx
+++ b/examples/output/phase0-write-example.xlsx
@@ -2,6 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr date1904="false"/>
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="Phase0" r:id="rId3" sheetId="1"/>
   </sheets>

--- a/examples/output/phase0-write-example.xlsx
+++ b/examples/output/phase0-write-example.xlsx
@@ -134,6 +134,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins bottom="0.7500" footer="0.3000" header="0.3000" left="0.7000" right="0.7000" top="0.7500"/>
 </worksheet>
 </file>